--- a/experiments/results/resnet34/CIFAR-100/ReAct+DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/ReAct+DICE/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -911,6 +911,55 @@
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>dice_p=90,ash_p=None,react_th=1.5,scale_th=5.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>84.93000000000001</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.5,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
